--- a/business_surveys/028_gaming_income_opportunities_survey--business_surveys.xlsx
+++ b/business_surveys/028_gaming_income_opportunities_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>welcome_to_the_survey</t>
+          <t>Welcome to the survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gaming_income</t>
+          <t>income_level</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>how_do_you_earn_money</t>
+          <t>What is your income level?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>income_level</t>
+          <t>income_from_gaming</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_is_your_income_level</t>
+          <t>How much do you earn from gaming?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>income_from_gaming</t>
+          <t>income_justification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how_much_do_you_earn_from_gaming</t>
+          <t>Why do you earn money through gaming?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>income_justification</t>
+          <t>additional_income</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>why_do_you_earn_money_through_gaming</t>
+          <t>Do you receive additional income from gaming?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gaming_motivations</t>
+          <t>time_spent_playing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_motivates_you_to_play</t>
+          <t>How much time do you spend playing games?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>additional_income</t>
+          <t>gaming_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>do_you_receive_additional_income</t>
+          <t>How often do you play games?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>survey_completion</t>
+          <t>gaming_communities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>that_is_all_for_today</t>
+          <t>What gaming communities do you belong to?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>time_spent_playing</t>
+          <t>gaming_partners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>how_much_time_do_you_spend_playing_games</t>
+          <t>Do you have gaming partners?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gaming_frequency</t>
+          <t>survey_participation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>how_often_do_you_play_games</t>
+          <t>How did you hear about this survey?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gaming_communities</t>
+          <t>gaming_streaming_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_gaming_communities_do_you_belong_to</t>
+          <t>How often do you stream games?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gaming_partners</t>
+          <t>gaming_streaming_platforms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>do_you_have_any_gaming_partners</t>
+          <t>Which streaming platforms do you use?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,297 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>survey_participation</t>
+          <t>gaming_tags</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>how_did_you_hear_about_this_survey</t>
+          <t>Do you have a tag on your stream?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>survey_completion</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>that_is_all_for_today</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>time_spent_streaming</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>how_much_time_do_you_spend_streaming</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>gaming_streaming_frequency</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>how_often_do_you_stream</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>streaming_platforms</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>which_streaming_platforms_do_you_use</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>gamer_tags</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>do_you_have_a_tag_on_your_stream</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>survey_completion</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>that_is_all_for_today</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>gaming_frequency</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>how_often_do_you_play_games</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>gaming_frequency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>how_often_do_you_play_games</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>gamer_tags</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>do_you_have_a_tag_on_your_stream</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>gaming_partners</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>do_you_have_any_gaming_partners</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>survey_completion</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>that_is_all_for_today</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>gaming_income</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>how_much_do_you_earn_from_gaming</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1126,51 +850,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gaming_income_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gaming_income_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gaming_income_choices</t>
+          <t>income_level_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1228,576 +952,355 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gaming_motivations_choices</t>
+          <t>additional_income_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>motivation_1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Motivation 1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gaming_motivations_choices</t>
+          <t>additional_income_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>motivation_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Motivation 2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gaming_motivations_choices</t>
+          <t>gaming_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>motivation_3</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Motivation 3</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>additional_income_choices</t>
+          <t>gaming_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>additional_income_choices</t>
+          <t>gaming_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gaming_frequency_choices</t>
+          <t>gaming_communities_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>community_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Community 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gaming_frequency_choices</t>
+          <t>gaming_communities_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>community_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Community 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gaming_frequency_choices</t>
+          <t>gaming_communities_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>community_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Community 3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gaming_communities_choices</t>
+          <t>gaming_partners_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>community_1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Community 1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gaming_communities_choices</t>
+          <t>gaming_partners_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>community_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Community 2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gaming_communities_choices</t>
+          <t>survey_participation_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>community_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Community 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gaming_partners_choices</t>
+          <t>survey_participation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gaming_partners_choices</t>
+          <t>survey_participation_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>survey_participation_choices</t>
+          <t>gaming_streaming_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>survey_participation_choices</t>
+          <t>gaming_streaming_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>survey_participation_choices</t>
+          <t>gaming_streaming_frequency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gaming_streaming_frequency_choices</t>
+          <t>gaming_streaming_platforms_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>platform_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Platform 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gaming_streaming_frequency_choices</t>
+          <t>gaming_streaming_platforms_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>platform_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Platform 2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gaming_streaming_frequency_choices</t>
+          <t>gaming_streaming_platforms_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>platform_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Platform 3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>streaming_platforms_choices</t>
+          <t>gaming_tags_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>platform_1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Platform 1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>streaming_platforms_choices</t>
+          <t>gaming_tags_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>platform_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Platform 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>streaming_platforms_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>platform_3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Platform 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>gamer_tags_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>gamer_tags_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>gaming_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>gaming_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sometimes</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sometimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>gaming_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>gaming_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>gaming_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sometimes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Sometimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>gaming_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>gamer_tags_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>gamer_tags_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>gaming_partners_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>gaming_partners_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>False</t>
         </is>
